--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:27:44+00:00</t>
+    <t>2026-04-30T07:27:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T07:27:20+00:00</t>
+    <t>2026-04-30T08:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:16:21+00:00</t>
+    <t>2026-04-30T08:30:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="360">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:30:02+00:00</t>
+    <t>2026-04-30T08:50:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -973,13 +973,77 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment</t>
   </si>
   <si>
-    <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
-  </si>
-  <si>
     <t>Spécialités ou compétences particulières du PS associées au créneau</t>
   </si>
   <si>
+    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
+  </si>
+  <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-practitioner-specialty</t>
+  </si>
+  <si>
+    <t>Slot.specialty.id</t>
+  </si>
+  <si>
+    <t>Slot.specialty.extension</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding</t>
+  </si>
+  <si>
+    <t>specialtycoding</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.id</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.id</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.extension</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.extension</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.system</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.system</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.version</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.version</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.code</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.code</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.display</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.display</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding:specialtycoding.userSelected</t>
+  </si>
+  <si>
+    <t>Slot.specialty.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Slot.specialty.text</t>
   </si>
   <si>
     <t>Slot.appointmentType</t>
@@ -1361,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.66796875" customWidth="true" bestFit="true"/>
@@ -5718,20 +5782,18 @@
         <v>72</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>96</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>72</v>
@@ -5756,13 +5818,13 @@
         <v>72</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>315</v>
+        <v>72</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>316</v>
+        <v>72</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>72</v>
@@ -5780,7 +5842,7 @@
         <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>98</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>73</v>
@@ -5789,29 +5851,29 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
@@ -5820,19 +5882,19 @@
         <v>72</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
+        <v>103</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5870,39 +5932,39 @@
         <v>72</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>236</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5910,10 +5972,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5925,24 +5987,26 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>325</v>
+        <v>72</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>72</v>
@@ -5960,37 +6024,35 @@
         <v>72</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>327</v>
+        <v>72</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>322</v>
+        <v>260</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>92</v>
@@ -6001,21 +6063,23 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -6027,18 +6091,20 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>329</v>
+        <v>257</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>72</v>
       </c>
@@ -6062,11 +6128,9 @@
         <v>72</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
         <v>72</v>
       </c>
@@ -6086,13 +6150,13 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>92</v>
@@ -6103,10 +6167,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6114,7 +6178,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>80</v>
@@ -6126,20 +6190,18 @@
         <v>72</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>332</v>
+        <v>96</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>72</v>
@@ -6188,38 +6250,38 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>98</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>72</v>
@@ -6231,22 +6293,22 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>294</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>334</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Q48" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
         <v>72</v>
       </c>
@@ -6278,39 +6340,39 @@
         <v>72</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>108</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6318,7 +6380,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>80</v>
@@ -6330,21 +6392,23 @@
         <v>72</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>267</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>268</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>72</v>
       </c>
@@ -6392,7 +6456,7 @@
         <v>72</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>337</v>
+        <v>272</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
@@ -6404,6 +6468,1238 @@
         <v>92</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q60" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="R60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:50:01+00:00</t>
+    <t>2026-04-30T09:39:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:39:49+00:00</t>
+    <t>2026-04-30T09:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1017,6 +1017,9 @@
   </si>
   <si>
     <t>Slot.specialty.coding.system</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R38-SpecialiteOrdinale/FHIR/TRE-R38-SpecialiteOrdinale</t>
   </si>
   <si>
     <t>Slot.specialty.coding:specialtycoding.version</t>
@@ -6417,7 +6420,7 @@
         <v>72</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>72</v>
+        <v>324</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>72</v>
@@ -6473,10 +6476,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6575,10 +6578,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6679,10 +6682,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6783,10 +6786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6887,10 +6890,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6991,10 +6994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7020,10 +7023,10 @@
         <v>201</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>240</v>
@@ -7055,10 +7058,10 @@
         <v>160</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>72</v>
@@ -7076,7 +7079,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7093,10 +7096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7119,16 +7122,16 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7178,7 +7181,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7195,10 +7198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7224,10 +7227,10 @@
         <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>283</v>
@@ -7238,7 +7241,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>72</v>
@@ -7259,10 +7262,10 @@
         <v>138</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>72</v>
@@ -7280,7 +7283,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7297,10 +7300,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7326,13 +7329,13 @@
         <v>116</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7382,7 +7385,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7399,10 +7402,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7428,13 +7431,13 @@
         <v>116</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7484,7 +7487,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7501,10 +7504,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7530,10 +7533,10 @@
         <v>294</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7541,7 +7544,7 @@
         <v>72</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>72</v>
@@ -7586,7 +7589,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
@@ -7603,10 +7606,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7632,10 +7635,10 @@
         <v>95</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>283</v>
@@ -7688,7 +7691,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:58:38+00:00</t>
+    <t>2026-04-30T12:46:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:46:52+00:00</t>
+    <t>2026-04-30T13:16:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>72</v>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:16:04+00:00</t>
+    <t>2026-04-30T13:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:33:12+00:00</t>
+    <t>2026-04-30T13:47:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -999,6 +999,9 @@
   </si>
   <si>
     <t>specialtycoding</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-contact-relationship</t>
   </si>
   <si>
     <t>Slot.specialty.coding:specialtycoding.id</t>
@@ -6135,7 +6138,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>72</v>
@@ -6170,10 +6173,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6270,10 +6273,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6372,10 +6375,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6420,7 +6423,7 @@
         <v>72</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>72</v>
@@ -6476,10 +6479,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6578,10 +6581,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6682,10 +6685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6786,10 +6789,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6890,10 +6893,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6994,10 +6997,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7023,10 +7026,10 @@
         <v>201</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>240</v>
@@ -7058,10 +7061,10 @@
         <v>160</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>72</v>
@@ -7079,7 +7082,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7096,10 +7099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7122,16 +7125,16 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7181,7 +7184,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7198,10 +7201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7227,10 +7230,10 @@
         <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>283</v>
@@ -7241,7 +7244,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>72</v>
@@ -7262,10 +7265,10 @@
         <v>138</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>72</v>
@@ -7283,7 +7286,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7300,10 +7303,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7329,13 +7332,13 @@
         <v>116</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7385,7 +7388,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7402,10 +7405,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7431,13 +7434,13 @@
         <v>116</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7487,7 +7490,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7504,10 +7507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7533,10 +7536,10 @@
         <v>294</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7544,7 +7547,7 @@
         <v>72</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>72</v>
@@ -7589,7 +7592,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
@@ -7606,10 +7609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7635,10 +7638,10 @@
         <v>95</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>283</v>
@@ -7691,7 +7694,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="339">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:47:19+00:00</t>
+    <t>2026-04-30T14:01:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -973,83 +973,13 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment</t>
   </si>
   <si>
-    <t>Spécialités ou compétences particulières du PS associées au créneau</t>
+    <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-practitioner-specialty</t>
-  </si>
-  <si>
-    <t>Slot.specialty.id</t>
-  </si>
-  <si>
-    <t>Slot.specialty.extension</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding</t>
-  </si>
-  <si>
-    <t>specialtycoding</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-contact-relationship</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.id</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.id</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.extension</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.extension</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.system</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R38-SpecialiteOrdinale/FHIR/TRE-R38-SpecialiteOrdinale</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.version</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.version</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.code</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.code</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.display</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.display</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding:specialtycoding.userSelected</t>
-  </si>
-  <si>
-    <t>Slot.specialty.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Slot.specialty.text</t>
   </si>
   <si>
     <t>Slot.appointmentType</t>
@@ -1431,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.66796875" customWidth="true" bestFit="true"/>
@@ -5788,18 +5718,20 @@
         <v>72</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>96</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>72</v>
@@ -5824,13 +5756,13 @@
         <v>72</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>72</v>
+        <v>316</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>72</v>
@@ -5848,7 +5780,7 @@
         <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>73</v>
@@ -5857,29 +5789,29 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
@@ -5888,19 +5820,19 @@
         <v>72</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>104</v>
+        <v>321</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5938,39 +5870,39 @@
         <v>72</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>108</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>109</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5978,10 +5910,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5993,26 +5925,24 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>72</v>
+        <v>325</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>72</v>
@@ -6030,35 +5960,37 @@
         <v>72</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>72</v>
+        <v>326</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>72</v>
+        <v>327</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>92</v>
@@ -6069,23 +6001,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -6097,20 +6027,18 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>72</v>
       </c>
@@ -6134,11 +6062,13 @@
         <v>72</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>318</v>
+        <v>72</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>72</v>
@@ -6156,13 +6086,13 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>92</v>
@@ -6173,10 +6103,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6184,7 +6114,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>80</v>
@@ -6196,18 +6126,20 @@
         <v>72</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>72</v>
@@ -6256,38 +6188,38 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>98</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>72</v>
@@ -6299,22 +6231,22 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>102</v>
+        <v>334</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Q48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="R48" t="s" s="2">
         <v>72</v>
       </c>
@@ -6346,39 +6278,39 @@
         <v>72</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>108</v>
+        <v>333</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6386,7 +6318,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>80</v>
@@ -6398,23 +6330,21 @@
         <v>72</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
       </c>
@@ -6423,7 +6353,7 @@
         <v>72</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>325</v>
+        <v>72</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>72</v>
@@ -6462,7 +6392,7 @@
         <v>72</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
@@ -6474,1238 +6404,6 @@
         <v>92</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q60" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="R60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-FrSlotAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T14:01:16+00:00</t>
+    <t>2026-05-05T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -976,7 +976,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
+    <t>Spécialités ou compétences particulières du PS associées au créneau</t>
   </si>
   <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-practitioner-specialty</t>
